--- a/it_forms/011_new_user_request_form--it_forms.xlsx
+++ b/it_forms/011_new_user_request_form--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1171,8 +1171,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'option_1',_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'option_1', 'label': 'option_1'}</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'option_2',_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'option_2', 'label': 'option_2'}</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'option_3',_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'option_3', 'label': 'option_3'}</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'option_6_1',_'label':_'option_6_1'}</t>
+          <t>option_6_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'option_6_1', 'label': 'option_6_1'}</t>
+          <t>option 6 1</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'option_6_2',_'label':_'option_6_2'}</t>
+          <t>option_6_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'option_6_2', 'label': 'option_6_2'}</t>
+          <t>option 6 2</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'option_6_3',_'label':_'option_6_3'}</t>
+          <t>option_6_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'option_6_3', 'label': 'option_6_3'}</t>
+          <t>option 6 3</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'option_7_1',_'label':_'option_7_1'}</t>
+          <t>option_7_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'option_7_1', 'label': 'option_7_1'}</t>
+          <t>option 7 1</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'option_7_2',_'label':_'option_7_2'}</t>
+          <t>option_7_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'option_7_2', 'label': 'option_7_2'}</t>
+          <t>option 7 2</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'option_7_3',_'label':_'option_7_3'}</t>
+          <t>option_7_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'option_7_3', 'label': 'option_7_3'}</t>
+          <t>option 7 3</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'option_13_1',_'label':_'option_13_1'}</t>
+          <t>option_13_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'option_13_1', 'label': 'option_13_1'}</t>
+          <t>option 13 1</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'option_13_2',_'label':_'option_13_2'}</t>
+          <t>option_13_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'option_13_2', 'label': 'option_13_2'}</t>
+          <t>option 13 2</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'option_14_1',_'label':_'option_14_1'}</t>
+          <t>option_14_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'option_14_1', 'label': 'option_14_1'}</t>
+          <t>option 14 1</t>
         </is>
       </c>
     </row>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'option_14_2',_'label':_'option_14_2'}</t>
+          <t>option_14_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'option_14_2', 'label': 'option_14_2'}</t>
+          <t>option 14 2</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'option_15_1',_'label':_'option_15_1'}</t>
+          <t>option_15_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'option_15_1', 'label': 'option_15_1'}</t>
+          <t>option 15 1</t>
         </is>
       </c>
     </row>
@@ -1438,12 +1438,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'option_15_2',_'label':_'option_15_2'}</t>
+          <t>option_15_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'option_15_2', 'label': 'option_15_2'}</t>
+          <t>option 15 2</t>
         </is>
       </c>
     </row>
@@ -1455,12 +1455,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'option_16_1',_'label':_'option_16_1'}</t>
+          <t>option_16_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'option_16_1', 'label': 'option_16_1'}</t>
+          <t>option 16 1</t>
         </is>
       </c>
     </row>
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'option_16_2',_'label':_'option_16_2'}</t>
+          <t>option_16_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'option_16_2', 'label': 'option_16_2'}</t>
+          <t>option 16 2</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'option_16_3',_'label':_'option_16_3'}</t>
+          <t>option_16_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'option_16_3', 'label': 'option_16_3'}</t>
+          <t>option 16 3</t>
         </is>
       </c>
     </row>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'option_17_1',_'label':_'option_17_1'}</t>
+          <t>option_17_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'option_17_1', 'label': 'option_17_1'}</t>
+          <t>option 17 1</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'option_17_2',_'label':_'option_17_2'}</t>
+          <t>option_17_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'option_17_2', 'label': 'option_17_2'}</t>
+          <t>option 17 2</t>
         </is>
       </c>
     </row>
@@ -1540,12 +1540,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'option_17_3',_'label':_'option_17_3'}</t>
+          <t>option_17_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'option_17_3', 'label': 'option_17_3'}</t>
+          <t>option 17 3</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'option_18_1',_'label':_'option_18_1'}</t>
+          <t>option_18_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'option_18_1', 'label': 'option_18_1'}</t>
+          <t>option 18 1</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'option_18_2',_'label':_'option_18_2'}</t>
+          <t>option_18_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'option_18_2', 'label': 'option_18_2'}</t>
+          <t>option 18 2</t>
         </is>
       </c>
     </row>
@@ -1591,12 +1591,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'option_19_1',_'label':_'option_19_1'}</t>
+          <t>option_19_1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'option_19_1', 'label': 'option_19_1'}</t>
+          <t>option 19 1</t>
         </is>
       </c>
     </row>
@@ -1608,12 +1608,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'option_19_2',_'label':_'option_19_2'}</t>
+          <t>option_19_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'option_19_2', 'label': 'option_19_2'}</t>
+          <t>option 19 2</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'option_19_3',_'label':_'option_19_3'}</t>
+          <t>option_19_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'option_19_3', 'label': 'option_19_3'}</t>
+          <t>option 19 3</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'option_22_1',_'label':_'option_22_1'}</t>
+          <t>option_22_1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'option_22_1', 'label': 'option_22_1'}</t>
+          <t>option 22 1</t>
         </is>
       </c>
     </row>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'option_22_2',_'label':_'option_22_2'}</t>
+          <t>option_22_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'option_22_2', 'label': 'option_22_2'}</t>
+          <t>option 22 2</t>
         </is>
       </c>
     </row>
@@ -1676,12 +1676,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'option_22_3',_'label':_'option_22_3'}</t>
+          <t>option_22_3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'option_22_3', 'label': 'option_22_3'}</t>
+          <t>option 22 3</t>
         </is>
       </c>
     </row>
@@ -1693,12 +1693,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'option_23_1',_'label':_'option_23_1'}</t>
+          <t>option_23_1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'option_23_1', 'label': 'option_23_1'}</t>
+          <t>option 23 1</t>
         </is>
       </c>
     </row>
@@ -1710,12 +1710,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'option_23_2',_'label':_'option_23_2'}</t>
+          <t>option_23_2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'option_23_2', 'label': 'option_23_2'}</t>
+          <t>option 23 2</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'option_24_1',_'label':_'option_24_1'}</t>
+          <t>option_24_1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'option_24_1', 'label': 'option_24_1'}</t>
+          <t>option 24 1</t>
         </is>
       </c>
     </row>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'option_24_2',_'label':_'option_24_2'}</t>
+          <t>option_24_2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'option_24_2', 'label': 'option_24_2'}</t>
+          <t>option 24 2</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'option_25_1',_'label':_'option_25_1'}</t>
+          <t>option_25_1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'option_25_1', 'label': 'option_25_1'}</t>
+          <t>option 25 1</t>
         </is>
       </c>
     </row>
@@ -1778,12 +1778,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'option_25_2',_'label':_'option_25_2'}</t>
+          <t>option_25_2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'option_25_2', 'label': 'option_25_2'}</t>
+          <t>option 25 2</t>
         </is>
       </c>
     </row>
